--- a/InteractiveLab/subject sheet.xlsx
+++ b/InteractiveLab/subject sheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\InteractiveLabPOC\InteractiveLab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A1BF287-D7B6-4FE5-99D4-7125326D4E72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FB1F464-5526-4692-B89C-2921123C74F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="8880" xr2:uid="{B53095F0-0CA3-47DD-8DFC-30AAFD0743B8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B53095F0-0CA3-47DD-8DFC-30AAFD0743B8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="15">
   <si>
     <t>par id</t>
   </si>
@@ -427,7 +427,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9367AA3B-033F-4ED0-9BB0-CE6E39CDE760}">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.5546875" bestFit="1" customWidth="1"/>
@@ -600,9 +600,7 @@
       <c r="G7" s="1"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="1">
-        <v>7</v>
-      </c>
+      <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
@@ -612,91 +610,287 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
-        <v>8</v>
+        <v>101</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
+      <c r="D9" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
+      <c r="F9" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="G9" s="1"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
-        <v>9</v>
+        <v>102</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
+      <c r="D10" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
+      <c r="F10" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="G10" s="1"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
-        <v>10</v>
+        <v>103</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
+      <c r="D11" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
+      <c r="F11" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="G11" s="1"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
-        <v>11</v>
+        <v>104</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
+      <c r="D12" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
+      <c r="F12" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="G12" s="1"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
-        <v>12</v>
+        <v>105</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
+      <c r="D13" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
+      <c r="F13" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="G13" s="1"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
-        <v>13</v>
+        <v>106</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
+      <c r="D14" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
+      <c r="F14" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="G14" s="1"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
-        <v>14</v>
+        <v>107</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
+      <c r="D15" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
+      <c r="F15" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="G15" s="1"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
-        <v>15</v>
+        <v>108</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
+      <c r="D16" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
+      <c r="F16" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="G16" s="1"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <v>109</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <v>110</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
+        <v>111</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <v>112</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <v>113</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <v>114</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <v>115</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <v>116</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
+        <v>117</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
+        <v>118</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
+        <v>119</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
+        <v>120</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
